--- a/artfynd/A 8558-2024 artfynd.xlsx
+++ b/artfynd/A 8558-2024 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>115961543</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -792,12 +787,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -807,12 +802,7 @@
         <v>115961579</v>
       </c>
       <c r="B3" t="n">
-        <v>57943</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,12 +906,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -931,12 +921,7 @@
         <v>115961512</v>
       </c>
       <c r="B4" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,12 +1027,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 8558-2024 artfynd.xlsx
+++ b/artfynd/A 8558-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115961543</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115961579</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1036,8 +1051,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115961512</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>